--- a/data/italy/p4_modeling/2024-10-29/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-29/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,25 +615,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.06365662150601253</v>
+        <v>-0.4366239618652412</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02040145379025688</v>
+        <v>-0.4062027426197641</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000559022430976294</v>
+        <v>-0.1100430506891504</v>
       </c>
       <c r="E3" t="n">
-        <v>3.223762863555862</v>
+        <v>19.9641621529716</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01705694636802043</v>
+        <v>0.1056304875818603</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -655,16 +655,16 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(189, 30)</t>
+          <t>(189, 17)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.836065240417637</v>
+        <v>1.260043757707314</v>
       </c>
       <c r="O3" t="n">
         <v>72</v>
@@ -676,18 +676,174 @@
         <v>51</v>
       </c>
       <c r="R3" t="n">
+        <v>90</v>
+      </c>
+      <c r="S3" t="n">
+        <v>45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>54</v>
+      </c>
+      <c r="U3" t="n">
+        <v>89</v>
+      </c>
+      <c r="V3" t="n">
+        <v>47.08994708994709</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.06365662150601253</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.02040145379025688</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.000559022430976294</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.223762863555862</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01705694636802043</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>(189, 30)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.836065240417637</v>
+      </c>
+      <c r="O4" t="n">
+        <v>72</v>
+      </c>
+      <c r="P4" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>51</v>
+      </c>
+      <c r="R4" t="n">
         <v>76</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>65</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>48</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>82</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V4" t="n">
+        <v>43.38624338624339</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.01748600862966612</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03231304958956627</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.02625236955239028</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2.505496711452182</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.01325659635688985</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>(189, 22)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5897448082037314</v>
+      </c>
+      <c r="O5" t="n">
+        <v>72</v>
+      </c>
+      <c r="P5" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>51</v>
+      </c>
+      <c r="R5" t="n">
+        <v>75</v>
+      </c>
+      <c r="S5" t="n">
+        <v>51</v>
+      </c>
+      <c r="T5" t="n">
+        <v>63</v>
+      </c>
+      <c r="U5" t="n">
+        <v>82</v>
+      </c>
+      <c r="V5" t="n">
         <v>43.38624338624339</v>
       </c>
     </row>

--- a/data/italy/p4_modeling/2024-10-29/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-29/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,90 +446,105 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>roi_200</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>roi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>roi_por_partido</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>thr_prob_min_best</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>curva</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>param1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>param2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>normalized</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>odd_weight</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_sup_cap</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>X_shape_missing</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>model_name</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>% roi_100</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t># result 1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t># result 0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t># result 2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t># pred 1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t># pred 0</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t># pred 2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t># aciertos</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
@@ -540,77 +555,86 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.848470765551557</v>
+        <v>5.372110203996275</v>
       </c>
       <c r="C2" t="n">
-        <v>5.648163706715484</v>
+        <v>6.529050533976029</v>
       </c>
       <c r="D2" t="n">
-        <v>6.583894096762437</v>
+        <v>9.242793285674839</v>
       </c>
       <c r="E2" t="n">
-        <v>1322.732778716996</v>
+        <v>6.764036167689103</v>
       </c>
       <c r="F2" t="n">
-        <v>6.998586130777754</v>
+        <v>2080.947025029461</v>
       </c>
       <c r="G2" t="n">
+        <v>10.10168458752165</v>
+      </c>
+      <c r="H2" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(189, 9)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>(206, 9)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>SVC</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0.2390905246702857</v>
-      </c>
-      <c r="O2" t="n">
-        <v>72</v>
-      </c>
-      <c r="P2" t="n">
-        <v>66</v>
-      </c>
       <c r="Q2" t="n">
-        <v>51</v>
+        <v>0.5471904429218718</v>
       </c>
       <c r="R2" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="V2" t="n">
-        <v>44.97354497354497</v>
+        <v>58</v>
+      </c>
+      <c r="W2" t="n">
+        <v>68</v>
+      </c>
+      <c r="X2" t="n">
+        <v>94</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>45.63106796116505</v>
       </c>
     </row>
     <row r="3">
@@ -618,233 +642,347 @@
         <v>79</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4366239618652412</v>
+        <v>-0.5581803065248784</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.4062027426197641</v>
+        <v>-0.5520431489690834</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1100430506891504</v>
+        <v>-0.1234830732305324</v>
       </c>
       <c r="E3" t="n">
-        <v>19.9641621529716</v>
+        <v>0.1491405133657223</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1056304875818603</v>
+        <v>31.65275634495379</v>
       </c>
       <c r="G3" t="n">
+        <v>0.1536541570143388</v>
+      </c>
+      <c r="H3" t="n">
         <v>-0.25</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K3" t="b">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(189, 17)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>(206, 17)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>LogisticRegression</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>1.260043757707314</v>
-      </c>
-      <c r="O3" t="n">
-        <v>72</v>
-      </c>
-      <c r="P3" t="n">
-        <v>66</v>
-      </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>1.27833722291687</v>
       </c>
       <c r="R3" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S3" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="T3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="V3" t="n">
-        <v>47.08994708994709</v>
+        <v>49</v>
+      </c>
+      <c r="W3" t="n">
+        <v>61</v>
+      </c>
+      <c r="X3" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>48.05825242718447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.06365662150601253</v>
+        <v>0.2567016528036427</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02040145379025688</v>
+        <v>0.07603656125895228</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.000559022430976294</v>
+        <v>0.01876147918259212</v>
       </c>
       <c r="E4" t="n">
-        <v>3.223762863555862</v>
+        <v>0.09769784457467366</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01705694636802043</v>
+        <v>18.41064947878765</v>
       </c>
       <c r="G4" t="n">
+        <v>0.08937208484848372</v>
+      </c>
+      <c r="H4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(189, 30)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1.836065240417637</v>
-      </c>
-      <c r="O4" t="n">
-        <v>72</v>
-      </c>
-      <c r="P4" t="n">
-        <v>66</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>(206, 64)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>51</v>
+        <v>0.1753830442714999</v>
       </c>
       <c r="R4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="V4" t="n">
-        <v>43.38624338624339</v>
+        <v>44</v>
+      </c>
+      <c r="W4" t="n">
+        <v>70</v>
+      </c>
+      <c r="X4" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>50.48543689320388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.1442564990934898</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004354504018141228</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05662864359966108</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06778557471956226</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14.40549558831121</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06992959023452044</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>(206, 30)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>15.05914013242103</v>
+      </c>
+      <c r="R5" t="n">
+        <v>79</v>
+      </c>
+      <c r="S5" t="n">
+        <v>67</v>
+      </c>
+      <c r="T5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U5" t="n">
+        <v>80</v>
+      </c>
+      <c r="V5" t="n">
+        <v>70</v>
+      </c>
+      <c r="W5" t="n">
+        <v>56</v>
+      </c>
+      <c r="X5" t="n">
+        <v>91</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>44.1747572815534</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B5" t="n">
-        <v>-0.01748600862966612</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.03231304958956627</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.02625236955239028</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-2.505496711452182</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.01325659635688985</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="B6" t="n">
+        <v>0.1053214706444609</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.01237128053050696</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.003061964680977193</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0109727707391027</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.123681845592799</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02487224196889708</v>
+      </c>
+      <c r="H6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(189, 22)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>(206, 22)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>LogisticRegression</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>0.5897448082037314</v>
-      </c>
-      <c r="O5" t="n">
-        <v>72</v>
-      </c>
-      <c r="P5" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>51</v>
-      </c>
-      <c r="R5" t="n">
-        <v>75</v>
-      </c>
-      <c r="S5" t="n">
-        <v>51</v>
-      </c>
-      <c r="T5" t="n">
-        <v>63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>82</v>
-      </c>
-      <c r="V5" t="n">
-        <v>43.38624338624339</v>
+      <c r="Q6" t="n">
+        <v>3.010482415911867</v>
+      </c>
+      <c r="R6" t="n">
+        <v>79</v>
+      </c>
+      <c r="S6" t="n">
+        <v>67</v>
+      </c>
+      <c r="T6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" t="n">
+        <v>81</v>
+      </c>
+      <c r="V6" t="n">
+        <v>56</v>
+      </c>
+      <c r="W6" t="n">
+        <v>69</v>
+      </c>
+      <c r="X6" t="n">
+        <v>92</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>44.66019417475729</v>
       </c>
     </row>
   </sheetData>
